--- a/braskem_pe5/Proposta_Braskem_PE5_DEM.xlsx
+++ b/braskem_pe5/Proposta_Braskem_PE5_DEM.xlsx
@@ -2465,12 +2465,6 @@
       <c r="H9" t="n">
         <v>5</v>
       </c>
-      <c r="K9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8</v>
-      </c>
       <c r="N9" s="141" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
@@ -2484,6 +2478,9 @@
       <c r="E10" s="61" t="n"/>
       <c r="F10" s="73" t="n"/>
       <c r="G10" s="56" t="n"/>
+      <c r="L10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="B11" s="55" t="inlineStr">
@@ -2496,6 +2493,12 @@
       <c r="E11" s="62" t="n"/>
       <c r="F11" s="73" t="n"/>
       <c r="G11" s="56" t="n"/>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" thickBot="1">
       <c r="B12" s="55" t="inlineStr">
@@ -2508,6 +2511,12 @@
       <c r="E12" s="62" t="n"/>
       <c r="F12" s="73" t="n"/>
       <c r="G12" s="56" t="n"/>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" thickBot="1">
       <c r="B13" s="66" t="inlineStr">
@@ -2525,12 +2534,6 @@
       <c r="G13" s="56" t="n"/>
       <c r="H13" t="n">
         <v>15</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>20</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
@@ -2544,6 +2547,9 @@
       <c r="E14" s="73" t="n"/>
       <c r="F14" s="61" t="n"/>
       <c r="G14" s="56" t="n"/>
+      <c r="L14" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="B15" s="55" t="inlineStr">
@@ -2556,6 +2562,9 @@
       <c r="E15" s="73" t="n"/>
       <c r="F15" s="62" t="n"/>
       <c r="G15" s="56" t="n"/>
+      <c r="L15" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
       <c r="B16" s="55" t="inlineStr">
@@ -2568,6 +2577,12 @@
       <c r="E16" s="73" t="n"/>
       <c r="F16" s="62" t="n"/>
       <c r="G16" s="56" t="n"/>
+      <c r="K16" t="n">
+        <v>2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" thickBot="1">
       <c r="B17" s="66" t="inlineStr">
@@ -2586,12 +2601,6 @@
       <c r="H17" t="n">
         <v>5</v>
       </c>
-      <c r="K17" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8</v>
-      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="B18" s="55" t="inlineStr">
@@ -2604,6 +2613,9 @@
       <c r="E18" s="73" t="n"/>
       <c r="F18" s="73" t="n"/>
       <c r="G18" s="62" t="n"/>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="B19" s="55" t="inlineStr">
@@ -2616,6 +2628,12 @@
       <c r="E19" s="73" t="n"/>
       <c r="F19" s="73" t="n"/>
       <c r="G19" s="62" t="n"/>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" thickBot="1">
       <c r="B20" s="64" t="inlineStr">
@@ -2628,6 +2646,12 @@
       <c r="E20" s="73" t="n"/>
       <c r="F20" s="73" t="n"/>
       <c r="G20" s="62" t="n"/>
+      <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1" thickBot="1">
       <c r="B21" s="66" t="inlineStr">

--- a/braskem_pe5/Proposta_Braskem_PE5_DEM.xlsx
+++ b/braskem_pe5/Proposta_Braskem_PE5_DEM.xlsx
@@ -1630,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="12.75"/>
   <cols>
     <col width="2.85546875" customWidth="1" style="1" min="1" max="1"/>
@@ -1872,71 +1872,25 @@
       <c r="I17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="123" t="n"/>
-      <c r="C18" s="124" t="n"/>
-      <c r="D18" s="125" t="n"/>
-      <c r="E18" s="125" t="n"/>
-      <c r="F18" s="125" t="n"/>
-      <c r="G18" s="125" t="n"/>
+      <c r="B18" s="128" t="inlineStr">
+        <is>
+          <t>Objetivo: Identificar as causas e propor mitigações para o embuchamento (clogging) de pó de PEAD na rosca transportadora da unidade PE5 (RS), utilizando simulação pelo Método de Elementos Discretos (DEM) no Star-CCM+ 2506. Serão avaliados dois cenários: rosca de pá helicoidal contínua (padrão) e rosca cut-flight, com foco nas zonas de velocidade de partícula próxima a zero, indicativas de embuchamento.</t>
+        </is>
+      </c>
+      <c r="G18" s="124" t="n"/>
       <c r="I18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="21" t="n"/>
-      <c r="D19" s="111" t="n"/>
-      <c r="E19" s="23" t="n"/>
-      <c r="F19" s="126" t="n"/>
-      <c r="G19" s="127" t="n"/>
+      <c r="B19" s="128" t="inlineStr">
+        <is>
+          <t>Recursos: Empregaremos neste projeto uma equipe técnica de consultores experientes na solução de problemas industriais com o apoio de ferramentas de CAE avançadas da SIEMENS, como o STAR-CCM+, referência mundial na área de fluidodinâmica.</t>
+        </is>
+      </c>
+      <c r="G19" s="124" t="n"/>
       <c r="I19" s="14" t="n"/>
     </row>
     <row r="20" ht="13.9" customHeight="1">
       <c r="B20" s="128" t="inlineStr">
-        <is>
-          <t>Objetivo: Identificar as causas e propor mitigações para o embuchamento (clogging) de pó de PEAD na rosca transportadora da unidade PE5 (RS), utilizando simulação pelo Método de Elementos Discretos (DEM) no Star-CCM+ 2506. Serão avaliados dois cenários: rosca de pá helicoidal contínua (padrão) e rosca cut-flight, com foco nas zonas de velocidade de partícula próxima a zero, indicativas de embuchamento.</t>
-        </is>
-      </c>
-      <c r="G20" s="124" t="n"/>
-      <c r="I20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="13.9" customHeight="1">
-      <c r="B21" s="82" t="n"/>
-      <c r="G21" s="124" t="n"/>
-      <c r="I21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="82" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="129" t="n"/>
-      <c r="G22" s="130" t="n"/>
-      <c r="I22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="12.75" customHeight="1">
-      <c r="B23" s="128" t="inlineStr">
-        <is>
-          <t>Recursos: Empregaremos neste projeto uma equipe técnica de consultores experientes na solução de problemas industriais com o apoio de ferramentas de CAE avançadas da SIEMENS, como o STAR-CCM+, referência mundial na área de fluidodinâmica.</t>
-        </is>
-      </c>
-      <c r="G23" s="124" t="n"/>
-      <c r="I23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="12.75" customHeight="1">
-      <c r="B24" s="82" t="n"/>
-      <c r="G24" s="124" t="n"/>
-      <c r="I24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="129" t="n"/>
-      <c r="G25" s="130" t="n"/>
-      <c r="I25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="128" t="inlineStr">
         <is>
           <t>Escopo: A CAEXPERTS desenvolverá o estudo em 4 etapas, descritas a seguir:
 Na Etapa 1 (Configuração Inicial — 5 dias): Ajuste da geometria 3D da rosca com os parâmetros reais fornecidos pela Braskem (D_screw, D_shaft, pitch, RPM); configuração do domínio DEM no Star-CCM+ 2506 com física de contato Hertz-Mindlin e Liquid Bridge Force (Lian, 1993) para modelar a coesão hexano-PEAD; calibração dos parâmetros de partícula com base na granulometria do PEAD fornecida.
@@ -1945,277 +1899,118 @@
 Na Etapa 4 (Reunião Final Online — dia 25): Apresentação dos resultados e recomendações de mitigação do embuchamento à equipe técnica da Braskem PE5.</t>
         </is>
       </c>
-      <c r="G26" s="124" t="n"/>
-      <c r="I26" s="14" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="82" t="n"/>
-      <c r="G27" s="124" t="n"/>
-      <c r="I27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="82" t="n"/>
-      <c r="G28" s="124" t="n"/>
-      <c r="I28" s="14" t="n"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="82" t="n"/>
-      <c r="G29" s="124" t="n"/>
-      <c r="I29" s="14" t="n"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="82" t="n"/>
-      <c r="G30" s="124" t="n"/>
-      <c r="I30" s="14" t="n"/>
-    </row>
-    <row r="31">
-      <c r="B31" s="82" t="n"/>
-      <c r="G31" s="124" t="n"/>
-      <c r="I31" s="14" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="82" t="n"/>
-      <c r="G32" s="124" t="n"/>
-      <c r="I32" s="14" t="n"/>
-    </row>
-    <row r="33">
-      <c r="B33" s="82" t="n"/>
-      <c r="G33" s="124" t="n"/>
-      <c r="I33" s="14" t="n"/>
-    </row>
-    <row r="34">
-      <c r="B34" s="82" t="n"/>
-      <c r="G34" s="124" t="n"/>
-      <c r="I34" s="14" t="n"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="82" t="n"/>
-      <c r="G35" s="124" t="n"/>
-      <c r="I35" s="14" t="n"/>
-    </row>
-    <row r="36">
-      <c r="B36" s="82" t="n"/>
-      <c r="G36" s="124" t="n"/>
-      <c r="I36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="B37" s="82" t="n"/>
-      <c r="G37" s="124" t="n"/>
-      <c r="I37" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="82" t="n"/>
-      <c r="G38" s="124" t="n"/>
-      <c r="I38" s="14" t="n"/>
-    </row>
-    <row r="39">
-      <c r="B39" s="82" t="n"/>
-      <c r="G39" s="124" t="n"/>
-      <c r="I39" s="14" t="n"/>
-    </row>
-    <row r="40">
-      <c r="B40" s="82" t="n"/>
-      <c r="G40" s="124" t="n"/>
-      <c r="I40" s="14" t="n"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="82" t="n"/>
-      <c r="G41" s="124" t="n"/>
-      <c r="I41" s="14" t="n"/>
-    </row>
-    <row r="42">
-      <c r="B42" s="43" t="n"/>
-      <c r="C42" s="83" t="n"/>
-      <c r="D42" s="83" t="n"/>
-      <c r="E42" s="83" t="n"/>
-      <c r="F42" s="83" t="n"/>
-      <c r="G42" s="44" t="n"/>
-      <c r="I42" s="14" t="n"/>
-    </row>
-    <row r="43" ht="12.75" customHeight="1">
-      <c r="B43" s="128" t="inlineStr">
+      <c r="G20" s="124" t="n"/>
+      <c r="I20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="13.9" customHeight="1">
+      <c r="B21" s="128" t="inlineStr">
         <is>
           <t>Cronograma de Atividades: A execução do projeto está prevista para ser realizada em 25 dias, conforme cronograma de atividades em anexo. A primeira etapa se iniciará oficialmente a partir do dia subsequente ao recebimento dos documentos com os dados necessários ao projeto. Cada etapa está com a duração em dias prevista conforme indicado abaixo:
 Etapa 1: 5 dias;   Etapa 2: 15 dias;   Etapa 3: 5 dias;   Reunião Final: dia 25.</t>
         </is>
       </c>
-      <c r="G43" s="124" t="n"/>
-      <c r="I43" s="14" t="n"/>
-    </row>
-    <row r="44" ht="12.75" customHeight="1">
-      <c r="B44" s="82" t="n"/>
-      <c r="G44" s="124" t="n"/>
-      <c r="I44" s="14" t="n"/>
-    </row>
-    <row r="45" ht="12.75" customHeight="1">
-      <c r="B45" s="82" t="n"/>
-      <c r="G45" s="124" t="n"/>
-      <c r="I45" s="14" t="n"/>
-    </row>
-    <row r="46" ht="12.75" customHeight="1">
-      <c r="B46" s="82" t="n"/>
-      <c r="G46" s="124" t="n"/>
-      <c r="I46" s="14" t="n"/>
-    </row>
-    <row r="47">
-      <c r="B47" s="82" t="n"/>
-      <c r="G47" s="124" t="n"/>
-      <c r="I47" s="14" t="n"/>
-    </row>
-    <row r="48">
-      <c r="B48" s="85" t="n"/>
-      <c r="C48" s="86" t="n"/>
-      <c r="D48" s="86" t="n"/>
-      <c r="E48" s="86" t="n"/>
-      <c r="F48" s="86" t="n"/>
-      <c r="G48" s="87" t="n"/>
-      <c r="I48" s="14" t="n"/>
-    </row>
-    <row r="49" ht="13.9" customHeight="1">
-      <c r="B49" s="128" t="inlineStr">
+      <c r="G21" s="124" t="n"/>
+      <c r="I21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="128" t="inlineStr">
         <is>
           <t>Requisitos/Dados Necessários ao Projeto: Diâmetro externo da pá (D_screw, mm), diâmetro do eixo (D_shaft, mm), passo da hélice (pitch, mm) e RPM de operação; granulometria do pó de PEAD (D10, D50, D90) — alternativamente, confirmação de semelhança com pó de talco; densidade aparente do PEAD (bulk density, kg/m³); localização típica do embuchamento (início/meio/fim da rosca); tipo de rosca em operação (padrão ou cut-flight); e, se disponível, desenho técnico ou croqui com cotas e fotos do equipamento.</t>
         </is>
       </c>
-      <c r="G49" s="124" t="n"/>
-      <c r="I49" s="14" t="n"/>
-    </row>
-    <row r="50">
-      <c r="B50" s="82" t="n"/>
-      <c r="G50" s="124" t="n"/>
-      <c r="I50" s="14" t="n"/>
-    </row>
-    <row r="51">
-      <c r="B51" s="85" t="n"/>
-      <c r="C51" s="86" t="n"/>
-      <c r="D51" s="86" t="n"/>
-      <c r="E51" s="86" t="n"/>
-      <c r="F51" s="86" t="n"/>
-      <c r="G51" s="87" t="n"/>
-      <c r="I51" s="14" t="n"/>
-    </row>
-    <row r="52" ht="13.9" customHeight="1">
-      <c r="B52" s="128" t="inlineStr">
+      <c r="G22" s="124" t="n"/>
+      <c r="I22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="12.75" customHeight="1">
+      <c r="B23" s="128" t="inlineStr">
         <is>
           <t>Entregáveis do Projeto: Relatório técnico em formato .ppt contendo: geometria 3D da rosca simulada (arquivo STEP), campos de velocidade e distribuição de partículas DEM, identificação das zonas de embuchamento, comparação quantitativa entre rosca padrão e cut-flight, e recomendações de mitigação fundamentadas nos resultados das simulações.</t>
         </is>
       </c>
-      <c r="G52" s="124" t="n"/>
-      <c r="I52" s="14" t="n"/>
-    </row>
-    <row r="53">
-      <c r="B53" s="85" t="n"/>
-      <c r="C53" s="86" t="n"/>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="129" t="n"/>
-      <c r="G53" s="130" t="n"/>
-      <c r="I53" s="14" t="n"/>
-    </row>
-    <row r="54" ht="13.9" customHeight="1">
-      <c r="B54" s="128" t="inlineStr">
+      <c r="G23" s="124" t="n"/>
+      <c r="I23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="12.75" customHeight="1">
+      <c r="B24" s="128" t="inlineStr">
         <is>
           <t>Quem Somos: A CAEXPERTS é uma empresa especializada em digitalização da engenharia que conta com uma rede de consultores pioneiros da implantação de tecnologias de simulação computacional na indústria nacional. Somos parceiros tecnológicos da SIEMENS Digital Industries Software, onde contamos com um portifólio de ferramentas de CAE mais completo do mercado.</t>
         </is>
       </c>
-      <c r="G54" s="124" t="n"/>
-      <c r="I54" s="14" t="n"/>
-    </row>
-    <row r="55" ht="13.9" customHeight="1">
-      <c r="B55" s="82" t="n"/>
-      <c r="G55" s="124" t="n"/>
-      <c r="I55" s="14" t="n"/>
-    </row>
-    <row r="56" ht="12.75" customHeight="1">
-      <c r="B56" s="82" t="n"/>
-      <c r="G56" s="124" t="n"/>
-      <c r="I56" s="14" t="n"/>
-    </row>
-    <row r="57">
-      <c r="B57" s="39" t="n"/>
-      <c r="C57" s="40" t="n"/>
-      <c r="D57" s="40" t="n"/>
-      <c r="E57" s="40" t="n"/>
-      <c r="F57" s="40" t="n"/>
-      <c r="G57" s="41" t="n"/>
-      <c r="I57" s="14" t="n"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="B58" s="91" t="inlineStr">
+      <c r="G24" s="124" t="n"/>
+      <c r="I24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="91" t="inlineStr">
         <is>
           <t>INVESTIMENTO TOTAL</t>
         </is>
       </c>
-      <c r="C58" s="131" t="n"/>
-      <c r="D58" s="131" t="n"/>
-      <c r="E58" s="131" t="n"/>
-      <c r="F58" s="132">
+      <c r="C25" s="131" t="n"/>
+      <c r="D25" s="131" t="n"/>
+      <c r="E25" s="131" t="n"/>
+      <c r="F25" s="132">
         <f>G17</f>
         <v/>
       </c>
-      <c r="G58" s="133" t="n"/>
-      <c r="I58" s="14" t="n"/>
-    </row>
-    <row r="59">
-      <c r="B59" s="9" t="n"/>
-      <c r="C59" s="26" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="134" t="n"/>
-      <c r="I59" s="14" t="n"/>
-    </row>
-    <row r="60">
-      <c r="B60" s="34" t="inlineStr">
+      <c r="G25" s="133" t="n"/>
+      <c r="I25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="34" t="inlineStr">
         <is>
           <t>Observações:</t>
         </is>
       </c>
-      <c r="C60" s="15" t="n"/>
-      <c r="D60" s="16" t="n"/>
-      <c r="I60" s="14" t="n"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="96" t="inlineStr">
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="I26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="96" t="inlineStr">
         <is>
           <t>Condições de Pagamento: 30 dias.</t>
         </is>
       </c>
-      <c r="I61" s="14" t="n"/>
-    </row>
-    <row r="62">
-      <c r="B62" s="96" t="inlineStr">
+      <c r="I27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="96" t="inlineStr">
         <is>
           <t>Faturamento: Nota fiscal de serviços</t>
         </is>
       </c>
-      <c r="I62" s="14" t="n"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="135" t="inlineStr">
+      <c r="I28" s="14" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="135" t="inlineStr">
         <is>
           <t>Aceitação desta proposta via emissão de pedido de compras ou contrato específico</t>
         </is>
       </c>
-      <c r="C64" s="136" t="n"/>
-      <c r="D64" s="136" t="n"/>
-      <c r="E64" s="136" t="n"/>
-      <c r="F64" s="136" t="n"/>
-      <c r="G64" s="137" t="n"/>
-    </row>
-    <row r="67">
-      <c r="H67" s="17" t="n"/>
-    </row>
-    <row r="68">
-      <c r="H68" s="17" t="n"/>
-    </row>
-    <row r="73" ht="23.25" customHeight="1">
-      <c r="B73" s="88" t="inlineStr">
+      <c r="C29" s="136" t="n"/>
+      <c r="D29" s="136" t="n"/>
+      <c r="E29" s="136" t="n"/>
+      <c r="F29" s="136" t="n"/>
+      <c r="G29" s="137" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="88" t="inlineStr">
         <is>
           <t>ANEXO - CRONOGRAMA DE ATIVIDADES</t>
         </is>
       </c>
     </row>
+    <row r="43" ht="12.75" customHeight="1"/>
+    <row r="44" ht="12.75" customHeight="1"/>
+    <row r="45" ht="12.75" customHeight="1"/>
+    <row r="46" ht="12.75" customHeight="1"/>
+    <row r="49" ht="13.9" customHeight="1"/>
+    <row r="52" ht="13.9" customHeight="1"/>
+    <row r="54" ht="13.9" customHeight="1"/>
+    <row r="55" ht="13.9" customHeight="1"/>
+    <row r="56" ht="12.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="73" ht="23.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="E10:G10"/>

--- a/braskem_pe5/Proposta_Braskem_PE5_DEM.xlsx
+++ b/braskem_pe5/Proposta_Braskem_PE5_DEM.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposta" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,15 +20,23 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -51,11 +59,6 @@
       <color rgb="FF3F3F3F"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -207,6 +210,12 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -251,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="43">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -295,19 +304,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF3F3F3F"/>
@@ -354,30 +350,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF3F3F3F"/>
@@ -418,17 +390,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -667,26 +628,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -707,15 +648,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -739,21 +671,61 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3"/>
     <xf numFmtId="44" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="23" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3"/>
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="167" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -805,7 +777,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -817,7 +789,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
@@ -840,9 +812,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
@@ -851,34 +820,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -891,66 +860,63 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="30" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="31" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="26" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="27" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="23" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="29" pivotButton="0" quotePrefix="0" xfId="7"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="25" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="32" pivotButton="0" quotePrefix="1" xfId="7"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="28" pivotButton="0" quotePrefix="1" xfId="7"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="7">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="7"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="10"/>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
@@ -963,156 +929,91 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="10">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="24" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="24" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="24" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="10"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="17">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="16">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="21">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="21">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="22">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Saída" xfId="1" builtinId="21"/>
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
@@ -1124,6 +1025,17 @@
     <cellStyle name="Moeda 2" xfId="8"/>
     <cellStyle name="Porcentagem 3" xfId="9"/>
     <cellStyle name="Porcentagem" xfId="10" builtinId="5"/>
+    <cellStyle name="Saída 2" xfId="11"/>
+    <cellStyle name="Moeda 3" xfId="12"/>
+    <cellStyle name="Vírgula 3" xfId="13"/>
+    <cellStyle name="Porcentagem 2 2" xfId="14"/>
+    <cellStyle name="Vírgula 2 2" xfId="15"/>
+    <cellStyle name="Hiperlink 2" xfId="16"/>
+    <cellStyle name="Normal 2 2" xfId="17"/>
+    <cellStyle name="Moeda 2 2" xfId="18"/>
+    <cellStyle name="Porcentagem 3 2" xfId="19"/>
+    <cellStyle name="Porcentagem 4" xfId="20"/>
+    <cellStyle name="Normal 3" xfId="21"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors/>
@@ -1142,8 +1054,8 @@
     <to>
       <col>9</col>
       <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>142875</rowOff>
+      <row>56</row>
+      <rowOff>57150</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -1185,8 +1097,8 @@
     <to>
       <col>9</col>
       <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>142875</rowOff>
+      <row>56</row>
+      <rowOff>57150</rowOff>
     </to>
     <pic>
       <nvPicPr>
@@ -1630,26 +1542,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="0" defaultRowHeight="12.75"/>
   <cols>
-    <col width="2.85546875" customWidth="1" style="1" min="1" max="1"/>
-    <col width="65.7109375" customWidth="1" style="1" min="2" max="2"/>
-    <col width="18.85546875" customWidth="1" style="1" min="3" max="3"/>
-    <col width="10.85546875" customWidth="1" style="6" min="4" max="4"/>
-    <col width="8.42578125" customWidth="1" style="1" min="5" max="5"/>
-    <col width="12.5703125" customWidth="1" style="1" min="6" max="7"/>
-    <col hidden="1" width="12.42578125" customWidth="1" style="1" min="8" max="8"/>
-    <col width="4.140625" customWidth="1" style="1" min="9" max="9"/>
-    <col hidden="1" width="11.28515625" customWidth="1" style="1" min="10" max="10"/>
-    <col hidden="1" width="37" customWidth="1" style="1" min="11" max="11"/>
-    <col hidden="1" width="10.42578125" customWidth="1" style="1" min="12" max="12"/>
-    <col hidden="1" width="7.42578125" customWidth="1" style="1" min="13" max="13"/>
-    <col hidden="1" width="11.42578125" customWidth="1" style="116" min="14" max="14"/>
-    <col hidden="1" width="8.85546875" customWidth="1" style="1" min="15" max="16384"/>
+    <col width="2.85546875" customWidth="1" style="89" min="1" max="1"/>
+    <col width="65.7109375" customWidth="1" style="89" min="2" max="2"/>
+    <col width="18.85546875" customWidth="1" style="89" min="3" max="3"/>
+    <col width="10.85546875" customWidth="1" style="90" min="4" max="4"/>
+    <col width="8.42578125" customWidth="1" style="89" min="5" max="5"/>
+    <col width="12.5703125" customWidth="1" style="89" min="6" max="7"/>
+    <col hidden="1" width="12.42578125" customWidth="1" style="89" min="8" max="8"/>
+    <col width="4.140625" customWidth="1" style="89" min="9" max="9"/>
+    <col hidden="1" width="11.28515625" customWidth="1" style="89" min="10" max="10"/>
+    <col hidden="1" width="37" customWidth="1" style="89" min="11" max="11"/>
+    <col hidden="1" width="10.42578125" customWidth="1" style="89" min="12" max="12"/>
+    <col hidden="1" width="7.42578125" customWidth="1" style="89" min="13" max="13"/>
+    <col hidden="1" width="11.42578125" customWidth="1" style="19" min="14" max="14"/>
+    <col hidden="1" width="8.85546875" customWidth="1" style="89" min="15" max="15"/>
+    <col hidden="1" width="8.85546875" customWidth="1" style="89" min="16" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" customHeight="1">
+    <row r="1" ht="21" customHeight="1" s="117">
       <c r="B1" s="29" t="n"/>
       <c r="C1" s="2" t="n"/>
       <c r="D1" s="3" t="n"/>
@@ -1658,7 +1571,7 @@
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
     </row>
-    <row r="2" ht="21" customHeight="1">
+    <row r="2" ht="21" customHeight="1" s="117">
       <c r="B2" s="4" t="n"/>
       <c r="C2" s="5" t="n"/>
       <c r="D2" s="30" t="inlineStr">
@@ -1666,63 +1579,63 @@
           <t>DATA:</t>
         </is>
       </c>
-      <c r="E2" s="98" t="n">
+      <c r="E2" s="94" t="n">
         <v>46196</v>
       </c>
     </row>
-    <row r="3" ht="12.95" customHeight="1">
+    <row r="3" ht="12.95" customHeight="1" s="117">
       <c r="C3" s="7" t="n"/>
       <c r="D3" s="8" t="n"/>
     </row>
-    <row r="4" ht="12.95" customHeight="1">
+    <row r="4" ht="12.95" customHeight="1" s="117">
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="30" t="inlineStr">
         <is>
           <t>DE:</t>
         </is>
       </c>
-      <c r="E4" s="99" t="inlineStr">
-        <is>
-          <t>Gabriel Hernandez Rozo</t>
-        </is>
-      </c>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="117" t="n"/>
-    </row>
-    <row r="5" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A5" s="1" t="n"/>
+      <c r="E4" s="116" t="inlineStr">
+        <is>
+          <t>Ricardo Barbosa de Barros</t>
+        </is>
+      </c>
+      <c r="K4" s="83" t="n"/>
+      <c r="L4" s="83" t="n"/>
+      <c r="M4" s="83" t="n"/>
+      <c r="N4" s="18" t="n"/>
+    </row>
+    <row r="5" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A5" s="89" t="n"/>
       <c r="C5" s="4" t="n"/>
       <c r="D5" s="31" t="n"/>
-      <c r="E5" s="33" t="inlineStr">
-        <is>
-          <t>ghrozo97@gmail.com</t>
-        </is>
-      </c>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="33" t="n"/>
-      <c r="N5" s="117" t="n"/>
-    </row>
-    <row r="6" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A6" s="1" t="n"/>
+      <c r="E5" s="118" t="inlineStr">
+        <is>
+          <t>(48) 9 9919 3243</t>
+        </is>
+      </c>
+      <c r="F5" s="118" t="n"/>
+      <c r="G5" s="118" t="n"/>
+      <c r="N5" s="18" t="n"/>
+    </row>
+    <row r="6" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A6" s="89" t="n"/>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="97" t="inlineStr">
-        <is>
-          <t>CAExperts — Florianópolis/SC</t>
-        </is>
-      </c>
-      <c r="N6" s="117" t="n"/>
-    </row>
-    <row r="7" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A7" s="1" t="n"/>
+      <c r="E6" s="115" t="inlineStr">
+        <is>
+          <t>barros@caexperts.com.br</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A7" s="89" t="n"/>
       <c r="C7" s="4" t="n"/>
-      <c r="E7" s="97" t="n"/>
-      <c r="N7" s="117" t="n"/>
-    </row>
-    <row r="8" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A8" s="1" t="n"/>
+      <c r="E7" s="98" t="n"/>
+      <c r="N7" s="18" t="n"/>
+    </row>
+    <row r="8" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A8" s="89" t="n"/>
       <c r="B8" s="29" t="inlineStr">
         <is>
           <t>Razão Social: Creative Solutions Engenharia e Consultoria LTDA</t>
@@ -1734,15 +1647,15 @@
           <t>PARA:</t>
         </is>
       </c>
-      <c r="E8" s="100" t="inlineStr">
+      <c r="E8" s="110" t="inlineStr">
         <is>
           <t>Braskem S.A. — Unidade PE5 (RS)</t>
         </is>
       </c>
-      <c r="N8" s="117" t="n"/>
-    </row>
-    <row r="9" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A9" s="1" t="n"/>
+      <c r="N8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A9" s="89" t="n"/>
       <c r="B9" s="29" t="inlineStr">
         <is>
           <t>CNPJ: 15.806.919/0001-44 - Inscrição Estadual: 25.676.225-2</t>
@@ -1750,15 +1663,15 @@
       </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="101" t="inlineStr">
+      <c r="E9" s="96" t="inlineStr">
         <is>
           <t>Jeferson Diefenthaler</t>
         </is>
       </c>
-      <c r="N9" s="117" t="n"/>
-    </row>
-    <row r="10" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A10" s="1" t="n"/>
+      <c r="N9" s="18" t="n"/>
+    </row>
+    <row r="10" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A10" s="89" t="n"/>
       <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Rod Jose Carlos Daux, km 01 - Edifício CELTA, 3º andar - Sala 2.02</t>
@@ -1766,11 +1679,15 @@
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="102" t="inlineStr"/>
-      <c r="N10" s="117" t="n"/>
-    </row>
-    <row r="11" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A11" s="1" t="n"/>
+      <c r="E10" s="119" t="inlineStr">
+        <is>
+          <t>jeferson.diefenthaler@braskem.com</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="n"/>
+    </row>
+    <row r="11" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A11" s="89" t="n"/>
       <c r="B11" s="29" t="inlineStr">
         <is>
           <t>CEP: 88030-902 - Bairro João Paulo</t>
@@ -1778,11 +1695,11 @@
       </c>
       <c r="C11" s="4" t="n"/>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="97" t="inlineStr"/>
-      <c r="N11" s="117" t="n"/>
-    </row>
-    <row r="12" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A12" s="1" t="n"/>
+      <c r="E11" s="98" t="n"/>
+      <c r="N11" s="18" t="n"/>
+    </row>
+    <row r="12" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A12" s="89" t="n"/>
       <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Florianópolis – SC – Brasil</t>
@@ -1790,107 +1707,119 @@
       </c>
       <c r="C12" s="4" t="n"/>
       <c r="D12" s="4" t="n"/>
-      <c r="N12" s="117" t="n"/>
-    </row>
-    <row r="13" ht="12.95" customFormat="1" customHeight="1" s="9">
-      <c r="A13" s="1" t="n"/>
+      <c r="N12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="12.95" customFormat="1" customHeight="1" s="83">
+      <c r="A13" s="89" t="n"/>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="32" t="inlineStr">
         <is>
           <t>VÁLIDO ATÉ:</t>
         </is>
       </c>
-      <c r="E13" s="98">
+      <c r="E13" s="94">
         <f>E2+30</f>
         <v/>
       </c>
-      <c r="N13" s="117" t="n"/>
-    </row>
-    <row r="14" ht="12.95" customHeight="1">
+      <c r="N13" s="18" t="n"/>
+    </row>
+    <row r="14" ht="12.95" customHeight="1" s="117">
       <c r="B14" s="10" t="n"/>
       <c r="C14" s="11" t="n"/>
     </row>
-    <row r="15" ht="21" customHeight="1">
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="103" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="118" t="inlineStr">
+    <row r="15" ht="21" customHeight="1" s="117">
+      <c r="B15" s="86" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C16" s="119" t="n"/>
-      <c r="D16" s="76" t="inlineStr">
+      <c r="C15" s="87" t="n"/>
+      <c r="D15" s="74" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="E16" s="77" t="inlineStr">
+      <c r="E15" s="75" t="inlineStr">
         <is>
           <t>Quant.</t>
         </is>
       </c>
-      <c r="F16" s="78" t="inlineStr">
+      <c r="F15" s="76" t="inlineStr">
         <is>
           <t>Valor Unit.</t>
         </is>
       </c>
-      <c r="G16" s="78" t="inlineStr">
+      <c r="G15" s="76" t="inlineStr">
         <is>
           <t>Valor Total</t>
         </is>
       </c>
-      <c r="I16" s="13" t="n"/>
-    </row>
-    <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="120" t="inlineStr">
+      <c r="I15" s="13" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="117">
+      <c r="B16" s="107" t="inlineStr">
         <is>
           <t>Estudo de Embuchamento em Rosca Transportadora — Simulação DEM (PEAD + Hexano)</t>
         </is>
       </c>
-      <c r="C17" s="121" t="n"/>
-      <c r="D17" s="110" t="inlineStr">
+      <c r="C16" s="108" t="n"/>
+      <c r="D16" s="84" t="inlineStr">
         <is>
           <t>Serviço</t>
         </is>
       </c>
-      <c r="E17" s="110" t="n">
+      <c r="E16" s="84" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="122">
+      <c r="F16" s="93">
         <f>ROUND(Cronograma!O5,0)*1.1</f>
         <v/>
       </c>
-      <c r="G17" s="122">
+      <c r="G16" s="93">
         <f>F17</f>
         <v/>
       </c>
+      <c r="I16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="12.75" customHeight="1" s="117">
+      <c r="B17" s="109" t="n"/>
+      <c r="C17" s="91" t="n"/>
+      <c r="D17" s="85" t="n"/>
+      <c r="E17" s="85" t="n"/>
+      <c r="F17" s="85" t="n"/>
+      <c r="G17" s="85" t="n"/>
       <c r="I17" s="14" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="128" t="inlineStr">
-        <is>
-          <t>Objetivo: Identificar as causas e propor mitigações para o embuchamento (clogging) de pó de PEAD na rosca transportadora da unidade PE5 (RS), utilizando simulação pelo Método de Elementos Discretos (DEM) no Star-CCM+ 2506. Serão avaliados dois cenários: rosca de pá helicoidal contínua (padrão) e rosca cut-flight, com foco nas zonas de velocidade de partícula próxima a zero, indicativas de embuchamento.</t>
-        </is>
-      </c>
-      <c r="G18" s="124" t="n"/>
+      <c r="B18" s="88" t="inlineStr">
+        <is>
+          <t>Objetivo: Identificar as causas e propor mitigações para o embuchamento (clogging) de pó de PEAD na rosca transportadora da unidade PE5 (RS), utilizando simulação pelo Método de Elementos Discretos (DEM) no Star-CCM+. Serão avaliados dois cenários: rosca de pá helicoidal contínua (padrão) e rosca cut-flight, com foco nas zonas de velocidade de partícula próxima a zero, indicativas de embuchamento.</t>
+        </is>
+      </c>
+      <c r="G18" s="91" t="n"/>
       <c r="I18" s="14" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="128" t="inlineStr">
+      <c r="B19" s="92" t="n"/>
+      <c r="G19" s="91" t="n"/>
+      <c r="I19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="13.9" customHeight="1" s="117">
+      <c r="B20" s="88" t="inlineStr">
         <is>
           <t>Recursos: Empregaremos neste projeto uma equipe técnica de consultores experientes na solução de problemas industriais com o apoio de ferramentas de CAE avançadas da SIEMENS, como o STAR-CCM+, referência mundial na área de fluidodinâmica.</t>
         </is>
       </c>
-      <c r="G19" s="124" t="n"/>
-      <c r="I19" s="14" t="n"/>
-    </row>
-    <row r="20" ht="13.9" customHeight="1">
-      <c r="B20" s="128" t="inlineStr">
+      <c r="G20" s="91" t="n"/>
+      <c r="I20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="31.5" customHeight="1" s="117">
+      <c r="B21" s="92" t="n"/>
+      <c r="G21" s="91" t="n"/>
+      <c r="I21" s="14" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="88" t="inlineStr">
         <is>
           <t>Escopo: A CAEXPERTS desenvolverá o estudo em 4 etapas, descritas a seguir:
 Na Etapa 1 (Configuração Inicial — 5 dias): Ajuste da geometria 3D da rosca com os parâmetros reais fornecidos pela Braskem (D_screw, D_shaft, pitch, RPM); configuração do domínio DEM no Star-CCM+ 2506 com física de contato Hertz-Mindlin e Liquid Bridge Force (Lian, 1993) para modelar a coesão hexano-PEAD; calibração dos parâmetros de partícula com base na granulometria do PEAD fornecida.
@@ -1899,118 +1828,159 @@
 Na Etapa 4 (Reunião Final Online — dia 25): Apresentação dos resultados e recomendações de mitigação do embuchamento à equipe técnica da Braskem PE5.</t>
         </is>
       </c>
-      <c r="G20" s="124" t="n"/>
-      <c r="I20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="13.9" customHeight="1">
-      <c r="B21" s="128" t="inlineStr">
+      <c r="G22" s="91" t="n"/>
+      <c r="I22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="12.75" customHeight="1" s="117">
+      <c r="B23" s="92" t="n"/>
+      <c r="G23" s="91" t="n"/>
+      <c r="I23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="12.75" customHeight="1" s="117">
+      <c r="B24" s="88" t="inlineStr">
         <is>
           <t>Cronograma de Atividades: A execução do projeto está prevista para ser realizada em 25 dias, conforme cronograma de atividades em anexo. A primeira etapa se iniciará oficialmente a partir do dia subsequente ao recebimento dos documentos com os dados necessários ao projeto. Cada etapa está com a duração em dias prevista conforme indicado abaixo:
 Etapa 1: 5 dias;   Etapa 2: 15 dias;   Etapa 3: 5 dias;   Reunião Final: dia 25.</t>
         </is>
       </c>
-      <c r="G21" s="124" t="n"/>
-      <c r="I21" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="128" t="inlineStr">
+      <c r="G24" s="91" t="n"/>
+      <c r="I24" s="14" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="92" t="n"/>
+      <c r="G25" s="91" t="n"/>
+      <c r="I25" s="14" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="88" t="inlineStr">
         <is>
           <t>Requisitos/Dados Necessários ao Projeto: Diâmetro externo da pá (D_screw, mm), diâmetro do eixo (D_shaft, mm), passo da hélice (pitch, mm) e RPM de operação; granulometria do pó de PEAD (D10, D50, D90) — alternativamente, confirmação de semelhança com pó de talco; densidade aparente do PEAD (bulk density, kg/m³); localização típica do embuchamento (início/meio/fim da rosca); tipo de rosca em operação (padrão ou cut-flight); e, se disponível, desenho técnico ou croqui com cotas e fotos do equipamento.</t>
         </is>
       </c>
-      <c r="G22" s="124" t="n"/>
-      <c r="I22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="12.75" customHeight="1">
-      <c r="B23" s="128" t="inlineStr">
+      <c r="G26" s="91" t="n"/>
+      <c r="I26" s="14" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="92" t="n"/>
+      <c r="G27" s="91" t="n"/>
+      <c r="I27" s="14" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="88" t="inlineStr">
         <is>
           <t>Entregáveis do Projeto: Relatório técnico em formato .ppt contendo: geometria 3D da rosca simulada (arquivo STEP), campos de velocidade e distribuição de partículas DEM, identificação das zonas de embuchamento, comparação quantitativa entre rosca padrão e cut-flight, e recomendações de mitigação fundamentadas nos resultados das simulações.</t>
         </is>
       </c>
-      <c r="G23" s="124" t="n"/>
-      <c r="I23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="12.75" customHeight="1">
-      <c r="B24" s="128" t="inlineStr">
-        <is>
-          <t>Quem Somos: A CAEXPERTS é uma empresa especializada em digitalização da engenharia que conta com uma rede de consultores pioneiros da implantação de tecnologias de simulação computacional na indústria nacional. Somos parceiros tecnológicos da SIEMENS Digital Industries Software, onde contamos com um portifólio de ferramentas de CAE mais completo do mercado.</t>
-        </is>
-      </c>
-      <c r="G24" s="124" t="n"/>
-      <c r="I24" s="14" t="n"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="91" t="inlineStr">
-        <is>
-          <t>INVESTIMENTO TOTAL</t>
-        </is>
-      </c>
-      <c r="C25" s="131" t="n"/>
-      <c r="D25" s="131" t="n"/>
-      <c r="E25" s="131" t="n"/>
-      <c r="F25" s="132">
-        <f>G17</f>
-        <v/>
-      </c>
-      <c r="G25" s="133" t="n"/>
-      <c r="I25" s="14" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="34" t="inlineStr">
-        <is>
-          <t>Observações:</t>
-        </is>
-      </c>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="I26" s="14" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="96" t="inlineStr">
-        <is>
-          <t>Condições de Pagamento: 30 dias.</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="96" t="inlineStr">
-        <is>
-          <t>Faturamento: Nota fiscal de serviços</t>
-        </is>
-      </c>
+      <c r="G28" s="91" t="n"/>
       <c r="I28" s="14" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="135" t="inlineStr">
-        <is>
-          <t>Aceitação desta proposta via emissão de pedido de compras ou contrato específico</t>
-        </is>
-      </c>
-      <c r="C29" s="136" t="n"/>
-      <c r="D29" s="136" t="n"/>
-      <c r="E29" s="136" t="n"/>
-      <c r="F29" s="136" t="n"/>
-      <c r="G29" s="137" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="79" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="37" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="I29" s="14" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="88" t="inlineStr">
         <is>
+          <t>Quem Somos: A CAEXPERTS é uma empresa especializada em digitalização da engenharia que conta com uma rede de consultores pioneiros da implantação de tecnologias de simulação computacional na indústria nacional. Somos parceiros tecnológicos da SIEMENS Digital Industries Software, onde contamos com um portifólio de ferramentas de CAE mais completo do mercado.</t>
+        </is>
+      </c>
+      <c r="G30" s="91" t="n"/>
+      <c r="I30" s="14" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="92" t="n"/>
+      <c r="G31" s="91" t="n"/>
+      <c r="I31" s="14" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="103" t="inlineStr">
+        <is>
+          <t>INVESTIMENTO TOTAL</t>
+        </is>
+      </c>
+      <c r="C32" s="104" t="n"/>
+      <c r="D32" s="104" t="n"/>
+      <c r="E32" s="104" t="n"/>
+      <c r="F32" s="105">
+        <f>G17</f>
+        <v/>
+      </c>
+      <c r="G32" s="106" t="n"/>
+      <c r="I32" s="14" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="83" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="27" t="n"/>
+      <c r="G33" s="28" t="n"/>
+      <c r="I33" s="14" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>Observações:</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="I34" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="95" t="inlineStr">
+        <is>
+          <t>Condições de Pagamento: 30 dias.</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="n"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="95" t="inlineStr">
+        <is>
+          <t>Faturamento: Nota fiscal de serviços</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="B38" s="100" t="inlineStr">
+        <is>
+          <t>Aceitação desta proposta via emissão de pedido de compras ou contrato específico</t>
+        </is>
+      </c>
+      <c r="C38" s="101" t="n"/>
+      <c r="D38" s="101" t="n"/>
+      <c r="E38" s="101" t="n"/>
+      <c r="F38" s="101" t="n"/>
+      <c r="G38" s="102" t="n"/>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="97" t="inlineStr">
+        <is>
           <t>ANEXO - CRONOGRAMA DE ATIVIDADES</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="12.75" customHeight="1"/>
-    <row r="44" ht="12.75" customHeight="1"/>
-    <row r="45" ht="12.75" customHeight="1"/>
-    <row r="46" ht="12.75" customHeight="1"/>
-    <row r="49" ht="13.9" customHeight="1"/>
-    <row r="52" ht="13.9" customHeight="1"/>
-    <row r="54" ht="13.9" customHeight="1"/>
-    <row r="55" ht="13.9" customHeight="1"/>
-    <row r="56" ht="12.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="73" ht="23.25" customHeight="1"/>
+    <row r="43" ht="12.75" customHeight="1" s="117"/>
+    <row r="44" ht="12.75" customHeight="1" s="117"/>
+    <row r="45" ht="12.75" customHeight="1" s="117"/>
+    <row r="46" ht="12.75" customHeight="1" s="117"/>
+    <row r="49" ht="13.9" customHeight="1" s="117"/>
+    <row r="50" ht="34.5" customHeight="1" s="117"/>
+    <row r="52" ht="39.75" customHeight="1" s="117"/>
+    <row r="54" ht="13.9" customHeight="1" s="117"/>
+    <row r="55" ht="13.9" customHeight="1" s="117"/>
+    <row r="56" ht="12.75" customHeight="1" s="117"/>
+    <row r="58" ht="15.75" customHeight="1" s="117"/>
+    <row r="73" ht="23.25" customHeight="1" s="117"/>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="E10:G10"/>
@@ -2029,8 +1999,8 @@
     <mergeCell ref="E11:G11"/>
     <mergeCell ref="F15:G15"/>
     <mergeCell ref="F17:F18"/>
+    <mergeCell ref="E7:G7"/>
     <mergeCell ref="B64:G64"/>
-    <mergeCell ref="E7:G7"/>
     <mergeCell ref="B58:E58"/>
     <mergeCell ref="B54:G56"/>
     <mergeCell ref="B23:G24"/>
@@ -2059,500 +2029,619 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:R30"/>
+  <dimension ref="B2:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="63.28515625" customWidth="1" min="2" max="2"/>
-    <col width="5.140625" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="7" bestFit="1" customWidth="1" min="4" max="7"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="11.28515625" customWidth="1" min="9" max="9"/>
-    <col width="12.140625" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="13.28515625" bestFit="1" customWidth="1" min="11" max="11"/>
-    <col width="13.28515625" customWidth="1" min="12" max="13"/>
-    <col width="16.5703125" customWidth="1" min="14" max="14"/>
-    <col width="14.7109375" customWidth="1" min="15" max="15"/>
-    <col width="10.7109375" customWidth="1" min="16" max="17"/>
-    <col hidden="1" width="12.28515625" customWidth="1" min="18" max="18"/>
+    <col width="63.28515625" customWidth="1" style="117" min="2" max="2"/>
+    <col width="5.140625" bestFit="1" customWidth="1" style="117" min="3" max="3"/>
+    <col width="7" bestFit="1" customWidth="1" style="117" min="4" max="4"/>
+    <col width="8.7109375" customWidth="1" style="117" min="5" max="5"/>
+    <col width="7" bestFit="1" customWidth="1" style="117" min="6" max="6"/>
+    <col width="8.28515625" customWidth="1" style="117" min="7" max="7"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" style="117" min="8" max="8"/>
+    <col width="11.28515625" customWidth="1" style="117" min="9" max="9"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="117" min="10" max="10"/>
+    <col width="13.28515625" bestFit="1" customWidth="1" style="117" min="11" max="11"/>
+    <col width="13.28515625" customWidth="1" style="117" min="12" max="13"/>
+    <col width="16.5703125" customWidth="1" style="117" min="14" max="14"/>
+    <col width="14.7109375" customWidth="1" style="117" min="15" max="15"/>
+    <col width="10.7109375" customWidth="1" style="117" min="16" max="17"/>
+    <col hidden="1" width="12.28515625" customWidth="1" style="117" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="2" ht="13.5" customHeight="1" thickBot="1">
-      <c r="N2" s="46" t="n"/>
-      <c r="R2" s="45" t="inlineStr">
+    <row r="2" ht="13.5" customHeight="1" s="117" thickBot="1">
+      <c r="N2" s="45" t="n"/>
+      <c r="R2" s="44" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B3" s="57" t="inlineStr">
+    <row r="3" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B3" s="56" t="inlineStr">
         <is>
           <t>ATIVIDADES DO PROJETO:                   |                  ETAPAS:</t>
         </is>
       </c>
-      <c r="C3" s="58" t="n">
+      <c r="C3" s="57" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="59" t="n">
+      <c r="D3" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="59" t="n">
+      <c r="E3" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="59" t="n">
+      <c r="F3" s="58" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="60" t="n">
+      <c r="G3" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="K3" s="46" t="inlineStr">
+      <c r="K3" s="45" t="inlineStr">
         <is>
           <t>Marcus</t>
         </is>
       </c>
-      <c r="L3" s="46" t="inlineStr">
+      <c r="L3" s="45" t="inlineStr">
         <is>
           <t>Gabriel</t>
         </is>
       </c>
-      <c r="M3" s="45" t="n"/>
-      <c r="N3" s="46" t="inlineStr">
+      <c r="M3" s="44" t="n"/>
+      <c r="N3" s="45" t="inlineStr">
         <is>
           <t>Urgência</t>
         </is>
       </c>
-      <c r="O3" s="45" t="inlineStr">
+      <c r="O3" s="44" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
-      <c r="P3" s="50" t="n"/>
-      <c r="Q3" s="50" t="n"/>
-      <c r="R3" s="79" t="inlineStr">
+      <c r="P3" s="49" t="n"/>
+      <c r="Q3" s="49" t="n"/>
+      <c r="R3" s="77" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="B4" s="69" t="inlineStr">
+    <row r="4" ht="16.5" customHeight="1" s="117" thickBot="1" thickTop="1">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>Início de Projeto</t>
         </is>
       </c>
-      <c r="C4" s="70" t="inlineStr">
+      <c r="C4" s="68" t="inlineStr">
         <is>
           <t>dia 0</t>
         </is>
       </c>
-      <c r="D4" s="53" t="n"/>
-      <c r="E4" s="53" t="n"/>
-      <c r="F4" s="53" t="n"/>
-      <c r="G4" s="54" t="n"/>
-      <c r="N4" s="46" t="inlineStr">
+      <c r="D4" s="52" t="n"/>
+      <c r="E4" s="52" t="n"/>
+      <c r="F4" s="52" t="n"/>
+      <c r="G4" s="53" t="n"/>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" s="45" t="inlineStr">
         <is>
           <t>Total Eq. Téc.</t>
         </is>
       </c>
-      <c r="O4" s="138">
-        <f>SUM(K24:L24)</f>
-        <v/>
-      </c>
-      <c r="P4" s="50" t="n"/>
-      <c r="Q4" s="50" t="n"/>
-      <c r="R4" s="50" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="B5" s="63" t="n"/>
-      <c r="C5" s="72" t="n"/>
-      <c r="D5" s="61" t="n"/>
-      <c r="E5" s="73" t="n"/>
-      <c r="F5" s="73" t="n"/>
-      <c r="G5" s="56" t="n"/>
-      <c r="N5" s="46" t="inlineStr">
+      <c r="O4" s="51">
+        <f>SUM(K27:L27)</f>
+        <v/>
+      </c>
+      <c r="P4" s="49" t="n"/>
+      <c r="Q4" s="49" t="n"/>
+      <c r="R4" s="49" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="117">
+      <c r="B5" s="62" t="inlineStr">
+        <is>
+          <t>Recebimento das informações e documentos do projeto</t>
+        </is>
+      </c>
+      <c r="C5" s="70" t="n"/>
+      <c r="D5" s="60" t="n"/>
+      <c r="E5" s="71" t="n"/>
+      <c r="F5" s="71" t="n"/>
+      <c r="G5" s="55" t="n"/>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8</v>
+      </c>
+      <c r="N5" s="45" t="inlineStr">
         <is>
           <t>Total Projeto:</t>
         </is>
       </c>
-      <c r="O5" s="138">
+      <c r="O5" s="51">
         <f>O4/0.35</f>
         <v/>
       </c>
-      <c r="P5" s="139" t="n"/>
-      <c r="Q5" s="139" t="n"/>
-      <c r="R5" s="140" t="inlineStr">
+      <c r="P5" s="50" t="n"/>
+      <c r="Q5" s="50" t="n"/>
+      <c r="R5" s="78" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="55" t="n"/>
-      <c r="C6" s="72" t="n"/>
-      <c r="D6" s="62" t="n"/>
-      <c r="E6" s="73" t="n"/>
-      <c r="F6" s="73" t="n"/>
-      <c r="G6" s="56" t="n"/>
-      <c r="N6" s="50" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="117">
+      <c r="B6" s="54" t="inlineStr">
+        <is>
+          <t>Revisão da literatura normas aplicáveis e documentos do projeto</t>
+        </is>
+      </c>
+      <c r="C6" s="70" t="n"/>
+      <c r="D6" s="61" t="n"/>
+      <c r="E6" s="71" t="n"/>
+      <c r="F6" s="71" t="n"/>
+      <c r="G6" s="55" t="n"/>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="49" t="inlineStr">
         <is>
           <t>Rateio</t>
         </is>
       </c>
-      <c r="O6" s="84" t="n">
+      <c r="O6" s="82" t="n">
         <v>0.35</v>
       </c>
-      <c r="P6" s="139" t="n"/>
-      <c r="Q6" s="139" t="n"/>
-      <c r="R6" s="140" t="inlineStr">
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="50" t="n"/>
+      <c r="R6" s="78" t="inlineStr">
         <is>
           <t>CFD + DEM</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="55" t="n"/>
-      <c r="C7" s="72" t="n"/>
-      <c r="D7" s="62" t="n"/>
-      <c r="E7" s="73" t="n"/>
-      <c r="F7" s="73" t="n"/>
-      <c r="G7" s="56" t="n"/>
-      <c r="N7" s="50" t="n"/>
-      <c r="O7" s="139" t="n"/>
-      <c r="P7" s="139" t="n"/>
-      <c r="Q7" s="139" t="n"/>
-      <c r="R7" s="140" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="117">
+      <c r="B7" s="54" t="inlineStr">
+        <is>
+          <t>Simplificação do CAD 3D para simulação CFD</t>
+        </is>
+      </c>
+      <c r="C7" s="70" t="n"/>
+      <c r="D7" s="61" t="n"/>
+      <c r="E7" s="71" t="n"/>
+      <c r="F7" s="71" t="n"/>
+      <c r="G7" s="55" t="n"/>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" s="49" t="n"/>
+      <c r="O7" s="50" t="n"/>
+      <c r="P7" s="50" t="n"/>
+      <c r="Q7" s="50" t="n"/>
+      <c r="R7" s="78" t="inlineStr">
         <is>
           <t>FEA</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B8" s="55" t="n"/>
-      <c r="C8" s="72" t="n"/>
-      <c r="D8" s="62" t="n"/>
-      <c r="E8" s="73" t="n"/>
-      <c r="F8" s="73" t="n"/>
-      <c r="G8" s="56" t="n"/>
-      <c r="N8" s="50" t="n"/>
-      <c r="O8" s="139" t="n"/>
-      <c r="P8" s="139" t="n"/>
-      <c r="Q8" s="139" t="n"/>
-      <c r="R8" s="140" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="117">
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>Definição das premissas e dos cenários de análise</t>
+        </is>
+      </c>
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="61" t="n"/>
+      <c r="E8" s="71" t="n"/>
+      <c r="F8" s="71" t="n"/>
+      <c r="G8" s="55" t="n"/>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="49" t="n"/>
+      <c r="O8" s="50" t="n"/>
+      <c r="P8" s="50" t="n"/>
+      <c r="Q8" s="50" t="n"/>
+      <c r="R8" s="78" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="117">
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>Criação da planilha de projeto</t>
+        </is>
+      </c>
+      <c r="C9" s="70" t="n"/>
+      <c r="D9" s="61" t="n"/>
+      <c r="E9" s="71" t="n"/>
+      <c r="F9" s="71" t="n"/>
+      <c r="G9" s="55" t="n"/>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="49" t="n"/>
+      <c r="O9" s="50" t="n"/>
+      <c r="P9" s="50" t="n"/>
+      <c r="Q9" s="50" t="n"/>
+      <c r="R9" s="78" t="n"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>Kick-off Meeting</t>
+        </is>
+      </c>
+      <c r="C10" s="70" t="n"/>
+      <c r="D10" s="61" t="n"/>
+      <c r="E10" s="71" t="n"/>
+      <c r="F10" s="71" t="n"/>
+      <c r="G10" s="55" t="n"/>
+      <c r="N10" s="49" t="n"/>
+      <c r="O10" s="50" t="n"/>
+      <c r="P10" s="50" t="n"/>
+      <c r="Q10" s="50" t="n"/>
+      <c r="R10" s="78" t="inlineStr">
         <is>
           <t>EMAG</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B9" s="66" t="inlineStr">
+    <row r="11" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B11" s="64" t="inlineStr">
         <is>
           <t>Configuração Inicial</t>
         </is>
       </c>
-      <c r="C9" s="67" t="n"/>
-      <c r="D9" s="70">
-        <f>"+" &amp; $H9 &amp; " dias"</f>
-        <v/>
-      </c>
-      <c r="E9" s="73" t="n"/>
-      <c r="F9" s="73" t="n"/>
-      <c r="G9" s="56" t="n"/>
-      <c r="H9" t="n">
+      <c r="C11" s="65" t="n"/>
+      <c r="D11" s="68">
+        <f>"+" &amp; $H11 &amp; " dias"</f>
+        <v/>
+      </c>
+      <c r="E11" s="71" t="n"/>
+      <c r="F11" s="71" t="n"/>
+      <c r="G11" s="55" t="n"/>
+      <c r="H11" t="n">
         <v>5</v>
       </c>
-      <c r="N9" s="141" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="63" t="inlineStr">
+      <c r="N11" s="46" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="117">
+      <c r="B12" s="62" t="inlineStr">
         <is>
           <t>Ajuste da geometria 3D (D_screw, D_shaft, pitch) com parâmetros reais Braskem</t>
         </is>
       </c>
-      <c r="C10" s="65" t="n"/>
-      <c r="D10" s="73" t="n"/>
-      <c r="E10" s="61" t="n"/>
-      <c r="F10" s="73" t="n"/>
-      <c r="G10" s="56" t="n"/>
-      <c r="L10" t="n">
+      <c r="C12" s="63" t="n"/>
+      <c r="D12" s="71" t="n"/>
+      <c r="E12" s="60" t="n"/>
+      <c r="F12" s="71" t="n"/>
+      <c r="G12" s="55" t="n"/>
+      <c r="K12" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="55" t="inlineStr">
-        <is>
-          <t>Setup DEM no Star-CCM+ 2506: Hertz-Mindlin + Liquid Bridge Force (Lian, 1993)</t>
-        </is>
-      </c>
-      <c r="C11" s="73" t="n"/>
-      <c r="D11" s="73" t="n"/>
-      <c r="E11" s="62" t="n"/>
-      <c r="F11" s="73" t="n"/>
-      <c r="G11" s="56" t="n"/>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B12" s="55" t="inlineStr">
-        <is>
-          <t>Calibração dos parâmetros de partícula (granulometria + bulk density do PEAD)</t>
-        </is>
-      </c>
-      <c r="C12" s="73" t="n"/>
-      <c r="D12" s="73" t="n"/>
-      <c r="E12" s="62" t="n"/>
-      <c r="F12" s="73" t="n"/>
-      <c r="G12" s="56" t="n"/>
-      <c r="K12" t="n">
-        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B13" s="66" t="inlineStr">
+    <row r="13" ht="15" customHeight="1" s="117">
+      <c r="B13" s="54" t="inlineStr">
+        <is>
+          <t>Setup DEM no Star-CCM+</t>
+        </is>
+      </c>
+      <c r="C13" s="71" t="n"/>
+      <c r="D13" s="71" t="n"/>
+      <c r="E13" s="61" t="n"/>
+      <c r="F13" s="71" t="n"/>
+      <c r="G13" s="55" t="n"/>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B14" s="54" t="inlineStr">
+        <is>
+          <t>Calibração dos parâmetros de partícula (granulometria + bulk density do PEAD)</t>
+        </is>
+      </c>
+      <c r="C14" s="71" t="n"/>
+      <c r="D14" s="71" t="n"/>
+      <c r="E14" s="61" t="n"/>
+      <c r="F14" s="71" t="n"/>
+      <c r="G14" s="55" t="n"/>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B15" s="64" t="inlineStr">
         <is>
           <t>Simulações dos Cenários</t>
         </is>
       </c>
-      <c r="C13" s="68" t="n"/>
-      <c r="D13" s="68" t="n"/>
-      <c r="E13" s="70">
-        <f>"+" &amp; $H13 &amp; " dias"</f>
-        <v/>
-      </c>
-      <c r="F13" s="73" t="n"/>
-      <c r="G13" s="56" t="n"/>
-      <c r="H13" t="n">
+      <c r="C15" s="66" t="n"/>
+      <c r="D15" s="66" t="n"/>
+      <c r="E15" s="68">
+        <f>"+" &amp; $H15 &amp; " dias"</f>
+        <v/>
+      </c>
+      <c r="F15" s="71" t="n"/>
+      <c r="G15" s="55" t="n"/>
+      <c r="H15" t="n">
         <v>15</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="63" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="117">
+      <c r="B16" s="62" t="inlineStr">
         <is>
           <t>Caso 1 — Rosca padrão: análise de zonas de velocidade ≈ 0 (embuchamento)</t>
         </is>
       </c>
-      <c r="C14" s="73" t="n"/>
-      <c r="D14" s="73" t="n"/>
-      <c r="E14" s="73" t="n"/>
-      <c r="F14" s="61" t="n"/>
-      <c r="G14" s="56" t="n"/>
-      <c r="L14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="55" t="inlineStr">
-        <is>
-          <t>Caso 2 — Rosca cut-flight: comparação com o caso base</t>
-        </is>
-      </c>
-      <c r="C15" s="73" t="n"/>
-      <c r="D15" s="73" t="n"/>
-      <c r="E15" s="73" t="n"/>
-      <c r="F15" s="62" t="n"/>
-      <c r="G15" s="56" t="n"/>
-      <c r="L15" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B16" s="55" t="inlineStr">
-        <is>
-          <t>Análise de campos de pressão e tensão sobre as partículas DEM</t>
-        </is>
-      </c>
-      <c r="C16" s="73" t="n"/>
-      <c r="D16" s="73" t="n"/>
-      <c r="E16" s="73" t="n"/>
-      <c r="F16" s="62" t="n"/>
-      <c r="G16" s="56" t="n"/>
+      <c r="C16" s="71" t="n"/>
+      <c r="D16" s="71" t="n"/>
+      <c r="E16" s="71" t="n"/>
+      <c r="F16" s="60" t="n"/>
+      <c r="G16" s="55" t="n"/>
       <c r="K16" t="n">
         <v>2</v>
       </c>
       <c r="L16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="117">
+      <c r="B17" s="54" t="inlineStr">
+        <is>
+          <t>Caso 2 — Rosca cut-flight: comparação com o caso base</t>
+        </is>
+      </c>
+      <c r="C17" s="71" t="n"/>
+      <c r="D17" s="71" t="n"/>
+      <c r="E17" s="71" t="n"/>
+      <c r="F17" s="61" t="n"/>
+      <c r="G17" s="55" t="n"/>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B18" s="54" t="inlineStr">
+        <is>
+          <t>Análise de campos de pressão sobre as partículas DEM</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="n"/>
+      <c r="D18" s="71" t="n"/>
+      <c r="E18" s="71" t="n"/>
+      <c r="F18" s="61" t="n"/>
+      <c r="G18" s="55" t="n"/>
+      <c r="K18" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B17" s="66" t="inlineStr">
+    <row r="19" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B19" s="64" t="inlineStr">
         <is>
           <t>Finalização</t>
         </is>
       </c>
-      <c r="C17" s="68" t="n"/>
-      <c r="D17" s="68" t="n"/>
-      <c r="E17" s="68" t="n"/>
-      <c r="F17" s="70">
-        <f>"+" &amp; $H17 &amp; " dias"</f>
-        <v/>
-      </c>
-      <c r="G17" s="56" t="n"/>
-      <c r="H17" t="n">
+      <c r="C19" s="66" t="n"/>
+      <c r="D19" s="66" t="n"/>
+      <c r="E19" s="66" t="n"/>
+      <c r="F19" s="68">
+        <f>"+" &amp; $H19 &amp; " dias"</f>
+        <v/>
+      </c>
+      <c r="G19" s="55" t="n"/>
+      <c r="H19" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="55" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="117">
+      <c r="B20" s="54" t="inlineStr">
         <is>
           <t>Pós-processamento: campos de velocidade, pressão e distribuição de partículas</t>
         </is>
       </c>
-      <c r="C18" s="73" t="n"/>
-      <c r="D18" s="73" t="n"/>
-      <c r="E18" s="73" t="n"/>
-      <c r="F18" s="73" t="n"/>
-      <c r="G18" s="62" t="n"/>
-      <c r="L18" t="n">
+      <c r="C20" s="71" t="n"/>
+      <c r="D20" s="71" t="n"/>
+      <c r="E20" s="71" t="n"/>
+      <c r="F20" s="71" t="n"/>
+      <c r="G20" s="61" t="n"/>
+      <c r="K20" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="55" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="117">
+      <c r="B21" s="54" t="inlineStr">
         <is>
           <t>Comparação quantitativa rosca padrão vs. cut-flight + identificação de zonas críticas</t>
         </is>
       </c>
-      <c r="C19" s="73" t="n"/>
-      <c r="D19" s="73" t="n"/>
-      <c r="E19" s="73" t="n"/>
-      <c r="F19" s="73" t="n"/>
-      <c r="G19" s="62" t="n"/>
-      <c r="K19" t="n">
+      <c r="C21" s="71" t="n"/>
+      <c r="D21" s="71" t="n"/>
+      <c r="E21" s="71" t="n"/>
+      <c r="F21" s="71" t="n"/>
+      <c r="G21" s="61" t="n"/>
+      <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L21" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B20" s="64" t="inlineStr">
+    <row r="22" ht="15" customHeight="1" s="117">
+      <c r="B22" s="54" t="inlineStr">
         <is>
           <t>Elaboração do relatório técnico em formato .ppt com metodologia e recomendações</t>
         </is>
       </c>
-      <c r="C20" s="73" t="n"/>
-      <c r="D20" s="73" t="n"/>
-      <c r="E20" s="73" t="n"/>
-      <c r="F20" s="73" t="n"/>
-      <c r="G20" s="62" t="n"/>
-      <c r="K20" t="n">
+      <c r="C22" s="71" t="n"/>
+      <c r="D22" s="71" t="n"/>
+      <c r="E22" s="71" t="n"/>
+      <c r="F22" s="71" t="n"/>
+      <c r="G22" s="61" t="n"/>
+      <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B23" s="114" t="inlineStr">
+        <is>
+          <t>Kit de Entregas</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="n"/>
+      <c r="D23" s="71" t="n"/>
+      <c r="E23" s="71" t="n"/>
+      <c r="F23" s="71" t="n"/>
+      <c r="G23" s="61" t="n"/>
+      <c r="K23" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B21" s="66" t="inlineStr">
+    <row r="24" ht="15.75" customHeight="1" s="117" thickBot="1">
+      <c r="B24" s="64" t="inlineStr">
         <is>
           <t>Reunião Final Online</t>
         </is>
       </c>
-      <c r="C21" s="68" t="n"/>
-      <c r="D21" s="68" t="n"/>
-      <c r="E21" s="68" t="n"/>
-      <c r="F21" s="68" t="n"/>
-      <c r="G21" s="70">
-        <f>"+" &amp; $H21 &amp; " dias"</f>
-        <v/>
-      </c>
-      <c r="H21" t="n">
+      <c r="C24" s="66" t="n"/>
+      <c r="D24" s="66" t="n"/>
+      <c r="E24" s="66" t="n"/>
+      <c r="F24" s="66" t="n"/>
+      <c r="G24" s="68">
+        <f>"+" &amp; $H24 &amp; " dias"</f>
+        <v/>
+      </c>
+      <c r="H24" t="n">
         <v>25</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K24" t="n">
         <v>2</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L24" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="22">
-      <c r="H22">
-        <f>SUM(H5:H21)</f>
-        <v/>
-      </c>
-      <c r="J22" s="46" t="inlineStr">
+    <row r="25">
+      <c r="H25">
+        <f>SUM(H5:H24)</f>
+        <v/>
+      </c>
+      <c r="J25" s="45" t="inlineStr">
         <is>
           <t>Total Horas</t>
         </is>
       </c>
-      <c r="K22">
-        <f>SUM(K4:K21)</f>
-        <v/>
-      </c>
-      <c r="L22">
-        <f>SUM(L4:L21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="J23" s="46" t="inlineStr">
+      <c r="K25">
+        <f>SUM(K4:K24)</f>
+        <v/>
+      </c>
+      <c r="L25">
+        <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="J26" s="45" t="inlineStr">
         <is>
           <t>Valor HH</t>
         </is>
       </c>
-      <c r="K23" s="141">
+      <c r="K26" s="46">
         <f>VLOOKUP(K3,'Tabela HH'!$H$4:$K$19,IF($O$3="Sim",4,3),0)</f>
         <v/>
       </c>
-      <c r="L23" s="141">
+      <c r="L26" s="46">
         <f>VLOOKUP(L3,'Tabela HH'!$H$4:$K$19,IF($O$3="Sim",4,3),0)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="K24" s="138">
-        <f>K22*VLOOKUP(K3,'Tabela HH'!$H$4:$K$19,IF($O$3="Sim",4,3),0)</f>
-        <v/>
-      </c>
-      <c r="L24" s="138">
-        <f>L22*VLOOKUP(L3,'Tabela HH'!$H$4:$K$19,IF($O$3="Sim",4,3),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="J25" s="46" t="inlineStr">
+    <row r="27">
+      <c r="K27" s="51">
+        <f>K25*VLOOKUP(K3,'Tabela HH'!$H$4:$K$19,IF($O$3="Sim",4,3),0)</f>
+        <v/>
+      </c>
+      <c r="L27" s="51">
+        <f>L25*VLOOKUP(L3,'Tabela HH'!$H$4:$K$19,IF($O$3="Sim",4,3),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="J28" s="45" t="inlineStr">
         <is>
           <t>% Calculado</t>
         </is>
       </c>
-      <c r="K25" s="142">
-        <f>K24/$O$4*$O$6</f>
-        <v/>
-      </c>
-      <c r="L25" s="142">
-        <f>L24/$O$4*$O$6</f>
-        <v/>
-      </c>
-      <c r="M25" s="74">
-        <f>SUM(K25:L25)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="45" t="n"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="45" t="n"/>
-      <c r="C27" s="45" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="45" t="n"/>
+      <c r="K28" s="73">
+        <f>K27/$O$4*$O$6</f>
+        <v/>
+      </c>
+      <c r="L28" s="73">
+        <f>L27/$O$4*$O$6</f>
+        <v/>
+      </c>
+      <c r="M28" s="72">
+        <f>SUM(K28:L28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="B29" s="45" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="B30" s="48" t="n"/>
+      <c r="C29" s="44" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="44" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="44" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="44" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="117">
+      <c r="B33" s="47" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation sqref="O3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>SimNao</formula1>
     </dataValidation>
@@ -2571,611 +2660,611 @@
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col width="16.140625" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13.28515625" customWidth="1" min="3" max="3"/>
-    <col width="12.85546875" customWidth="1" min="4" max="4"/>
-    <col width="10.5703125" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="9.85546875" bestFit="1" customWidth="1" min="8" max="8"/>
-    <col width="12.140625" bestFit="1" customWidth="1" min="9" max="9"/>
-    <col width="10.7109375" bestFit="1" customWidth="1" min="10" max="10"/>
-    <col width="11.28515625" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="16.140625" bestFit="1" customWidth="1" style="117" min="1" max="1"/>
+    <col width="12" customWidth="1" style="117" min="2" max="2"/>
+    <col width="13.28515625" customWidth="1" style="117" min="3" max="3"/>
+    <col width="12.85546875" customWidth="1" style="117" min="4" max="4"/>
+    <col width="10.5703125" bestFit="1" customWidth="1" style="117" min="5" max="5"/>
+    <col width="9.85546875" bestFit="1" customWidth="1" style="117" min="8" max="8"/>
+    <col width="12.140625" bestFit="1" customWidth="1" style="117" min="9" max="9"/>
+    <col width="10.7109375" bestFit="1" customWidth="1" style="117" min="10" max="10"/>
+    <col width="11.28515625" bestFit="1" customWidth="1" style="117" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="114" t="inlineStr">
+      <c r="A1" s="111" t="inlineStr">
         <is>
           <t>HH Projetos Geral; Acima de 60 dias de duração e HH de Viagens</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="n"/>
-      <c r="B2" s="50" t="inlineStr">
+      <c r="A2" s="48" t="n"/>
+      <c r="B2" s="49" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="C2" s="50" t="inlineStr">
+      <c r="C2" s="49" t="inlineStr">
         <is>
           <t>FEA</t>
         </is>
       </c>
-      <c r="D2" s="50" t="inlineStr">
+      <c r="D2" s="49" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
-      <c r="E2" s="50" t="inlineStr">
+      <c r="E2" s="49" t="inlineStr">
         <is>
           <t>EMAG</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>Estagiário</t>
         </is>
       </c>
-      <c r="B3" s="139" t="n">
+      <c r="B3" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="C3" s="139" t="n">
+      <c r="C3" s="50" t="n">
         <v>20</v>
       </c>
-      <c r="D3" s="139" t="n">
+      <c r="D3" s="50" t="n">
         <v>30</v>
       </c>
-      <c r="E3" s="139" t="n">
+      <c r="E3" s="50" t="n">
         <v>30</v>
       </c>
-      <c r="H3" s="46" t="inlineStr">
+      <c r="H3" s="45" t="inlineStr">
         <is>
           <t>Equipe</t>
         </is>
       </c>
-      <c r="I3" s="46" t="inlineStr">
+      <c r="I3" s="45" t="inlineStr">
         <is>
           <t>Senioridade</t>
         </is>
       </c>
-      <c r="J3" s="46" t="inlineStr">
+      <c r="J3" s="45" t="inlineStr">
         <is>
           <t>HH Normal</t>
         </is>
       </c>
-      <c r="K3" s="46" t="inlineStr">
+      <c r="K3" s="45" t="inlineStr">
         <is>
           <t>HH Urgente</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="B4" s="139" t="n">
+      <c r="B4" s="50" t="n">
         <v>30</v>
       </c>
-      <c r="C4" s="139" t="n">
+      <c r="C4" s="50" t="n">
         <v>40</v>
       </c>
-      <c r="D4" s="139" t="n">
+      <c r="D4" s="50" t="n">
         <v>50</v>
       </c>
-      <c r="E4" s="139" t="n">
+      <c r="E4" s="50" t="n">
         <v>50</v>
       </c>
-      <c r="G4" s="50" t="n"/>
-      <c r="H4" s="45" t="inlineStr">
+      <c r="G4" s="49" t="n"/>
+      <c r="H4" s="44" t="inlineStr">
         <is>
           <t>Marcus</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="44" t="inlineStr">
         <is>
           <t>Senior</t>
         </is>
       </c>
-      <c r="J4" s="141">
+      <c r="J4" s="46">
         <f>VLOOKUP(I4,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K4" s="141">
+      <c r="K4" s="46">
         <f>VLOOKUP(I4,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>Pleno</t>
         </is>
       </c>
-      <c r="B5" s="139" t="n">
+      <c r="B5" s="50" t="n">
         <v>50</v>
       </c>
-      <c r="C5" s="139" t="n">
+      <c r="C5" s="50" t="n">
         <v>60</v>
       </c>
-      <c r="D5" s="139">
+      <c r="D5" s="50">
         <f>75</f>
         <v/>
       </c>
-      <c r="E5" s="139" t="n">
+      <c r="E5" s="50" t="n">
         <v>75</v>
       </c>
-      <c r="G5" s="50" t="n"/>
-      <c r="H5" s="79" t="inlineStr">
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="77" t="inlineStr">
         <is>
           <t>Matheus</t>
         </is>
       </c>
-      <c r="I5" s="45" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>Pleno</t>
         </is>
       </c>
-      <c r="J5" s="141">
+      <c r="J5" s="46">
         <f>VLOOKUP(I5,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K5" s="141">
+      <c r="K5" s="46">
         <f>VLOOKUP(I5,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Senior</t>
         </is>
       </c>
-      <c r="B6" s="139" t="n">
+      <c r="B6" s="50" t="n">
         <v>80</v>
       </c>
-      <c r="C6" s="139">
+      <c r="C6" s="50">
         <f>90</f>
         <v/>
       </c>
-      <c r="D6" s="139">
+      <c r="D6" s="50">
         <f>100</f>
         <v/>
       </c>
-      <c r="E6" s="139" t="n">
+      <c r="E6" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="G6" s="50" t="n"/>
-      <c r="H6" s="45" t="inlineStr">
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="44" t="inlineStr">
         <is>
           <t>Otávio</t>
         </is>
       </c>
-      <c r="I6" s="45" t="inlineStr">
+      <c r="I6" s="44" t="inlineStr">
         <is>
           <t>Pleno</t>
         </is>
       </c>
-      <c r="J6" s="141">
+      <c r="J6" s="46">
         <f>VLOOKUP(I6,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K6" s="141">
+      <c r="K6" s="46">
         <f>VLOOKUP(I6,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="G7" s="50" t="n"/>
-      <c r="H7" s="45" t="inlineStr">
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="44" t="inlineStr">
         <is>
           <t>Humberto</t>
         </is>
       </c>
-      <c r="I7" s="45" t="inlineStr">
+      <c r="I7" s="44" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="J7" s="141">
+      <c r="J7" s="46">
         <f>VLOOKUP(I7,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K7" s="141">
+      <c r="K7" s="46">
         <f>VLOOKUP(I7,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="G8" s="50" t="n"/>
-      <c r="H8" s="45" t="inlineStr">
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="44" t="inlineStr">
         <is>
           <t>João</t>
         </is>
       </c>
-      <c r="I8" s="45" t="inlineStr">
+      <c r="I8" s="44" t="inlineStr">
         <is>
           <t>Estagiário</t>
         </is>
       </c>
-      <c r="J8" s="141">
+      <c r="J8" s="46">
         <f>VLOOKUP(I8,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K8" s="141">
+      <c r="K8" s="46">
         <f>VLOOKUP(I8,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="114" t="inlineStr">
+      <c r="A9" s="111" t="inlineStr">
         <is>
           <t>HH Projetos Geral; Abaixo de 60 dias de duração ou urgentes</t>
         </is>
       </c>
-      <c r="G9" s="50" t="n"/>
-      <c r="H9" s="45" t="inlineStr">
+      <c r="G9" s="49" t="n"/>
+      <c r="H9" s="44" t="inlineStr">
         <is>
           <t>Vitor</t>
         </is>
       </c>
-      <c r="I9" s="45" t="inlineStr">
+      <c r="I9" s="44" t="inlineStr">
         <is>
           <t>Estagiário</t>
         </is>
       </c>
-      <c r="J9" s="141">
+      <c r="J9" s="46">
         <f>VLOOKUP(I9,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K9" s="141">
+      <c r="K9" s="46">
         <f>VLOOKUP(I9,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="114" t="n"/>
-      <c r="B10" s="114" t="n"/>
-      <c r="C10" s="114" t="n"/>
-      <c r="D10" s="114" t="n"/>
-      <c r="E10" s="114" t="n"/>
-      <c r="G10" s="50" t="n"/>
-      <c r="H10" s="45" t="inlineStr">
+      <c r="A10" s="111" t="n"/>
+      <c r="B10" s="111" t="n"/>
+      <c r="C10" s="111" t="n"/>
+      <c r="D10" s="111" t="n"/>
+      <c r="E10" s="111" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="44" t="inlineStr">
         <is>
           <t>Gabriel</t>
         </is>
       </c>
-      <c r="I10" s="45" t="inlineStr">
+      <c r="I10" s="44" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="J10" s="141">
+      <c r="J10" s="46">
         <f>VLOOKUP(I10,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K10" s="141">
+      <c r="K10" s="46">
         <f>VLOOKUP(I10,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="49" t="n"/>
-      <c r="B11" s="50" t="inlineStr">
+      <c r="A11" s="48" t="n"/>
+      <c r="B11" s="49" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="C11" s="50" t="inlineStr">
+      <c r="C11" s="49" t="inlineStr">
         <is>
           <t>FEA</t>
         </is>
       </c>
-      <c r="D11" s="50" t="inlineStr">
+      <c r="D11" s="49" t="inlineStr">
         <is>
           <t>CFD</t>
         </is>
       </c>
-      <c r="E11" s="50" t="inlineStr">
+      <c r="E11" s="49" t="inlineStr">
         <is>
           <t>EMAG</t>
         </is>
       </c>
-      <c r="G11" s="114" t="n"/>
-      <c r="H11" s="79" t="inlineStr">
+      <c r="G11" s="111" t="n"/>
+      <c r="H11" s="77" t="inlineStr">
         <is>
           <t>Vinicius</t>
         </is>
       </c>
-      <c r="I11" s="45" t="inlineStr">
+      <c r="I11" s="44" t="inlineStr">
         <is>
           <t>Estagiário</t>
         </is>
       </c>
-      <c r="J11" s="141">
+      <c r="J11" s="46">
         <f>VLOOKUP(I11,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K11" s="141">
+      <c r="K11" s="46">
         <f>VLOOKUP(I11,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>Estagiário</t>
         </is>
       </c>
-      <c r="B12" s="139">
+      <c r="B12" s="50">
         <f>1.4*B3</f>
         <v/>
       </c>
-      <c r="C12" s="139">
+      <c r="C12" s="50">
         <f>1.4*C3</f>
         <v/>
       </c>
-      <c r="D12" s="139">
+      <c r="D12" s="50">
         <f>1.4*D3</f>
         <v/>
       </c>
-      <c r="E12" s="139">
+      <c r="E12" s="50">
         <f>1.4*E3</f>
         <v/>
       </c>
-      <c r="G12" s="50" t="n"/>
-      <c r="H12" s="45" t="inlineStr">
+      <c r="G12" s="49" t="n"/>
+      <c r="H12" s="44" t="inlineStr">
         <is>
           <t>Guerra</t>
         </is>
       </c>
-      <c r="I12" s="45" t="inlineStr">
+      <c r="I12" s="44" t="inlineStr">
         <is>
           <t>Externo</t>
         </is>
       </c>
-      <c r="J12" s="141" t="n">
+      <c r="J12" s="46" t="n">
         <v>120</v>
       </c>
-      <c r="K12" s="141" t="n">
+      <c r="K12" s="46" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="B13" s="139">
+      <c r="B13" s="50">
         <f>1.4*B4</f>
         <v/>
       </c>
-      <c r="C13" s="139">
+      <c r="C13" s="50">
         <f>1.4*C4</f>
         <v/>
       </c>
-      <c r="D13" s="139">
+      <c r="D13" s="50">
         <f>1.4*D4</f>
         <v/>
       </c>
-      <c r="E13" s="139">
+      <c r="E13" s="50">
         <f>1.4*E4</f>
         <v/>
       </c>
-      <c r="G13" s="50" t="n"/>
-      <c r="H13" s="45" t="inlineStr">
+      <c r="G13" s="49" t="n"/>
+      <c r="H13" s="44" t="inlineStr">
         <is>
           <t>Pedro</t>
         </is>
       </c>
-      <c r="I13" s="45" t="inlineStr">
+      <c r="I13" s="44" t="inlineStr">
         <is>
           <t>Pleno</t>
         </is>
       </c>
-      <c r="J13" s="141">
+      <c r="J13" s="46">
         <f>VLOOKUP(I13,$A$3:$E$6,5,0)</f>
         <v/>
       </c>
-      <c r="K13" s="141">
+      <c r="K13" s="46">
         <f>VLOOKUP(I13,$A$12:$E$15,5,0)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="inlineStr">
+      <c r="A14" s="49" t="inlineStr">
         <is>
           <t>Pleno</t>
         </is>
       </c>
-      <c r="B14" s="139">
+      <c r="B14" s="50">
         <f>1.4*B5</f>
         <v/>
       </c>
-      <c r="C14" s="139">
+      <c r="C14" s="50">
         <f>1.4*C5</f>
         <v/>
       </c>
-      <c r="D14" s="139">
+      <c r="D14" s="50">
         <f>1.4*D5</f>
         <v/>
       </c>
-      <c r="E14" s="139">
+      <c r="E14" s="50">
         <f>1.4*E5</f>
         <v/>
       </c>
-      <c r="G14" s="50" t="n"/>
-      <c r="H14" s="45" t="inlineStr">
+      <c r="G14" s="49" t="n"/>
+      <c r="H14" s="44" t="inlineStr">
         <is>
           <t>Diego</t>
         </is>
       </c>
-      <c r="I14" s="45" t="inlineStr">
+      <c r="I14" s="44" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="J14" s="141">
+      <c r="J14" s="46">
         <f>VLOOKUP(I14,$A$3:$E$6,4,0)</f>
         <v/>
       </c>
-      <c r="K14" s="141">
+      <c r="K14" s="46">
         <f>VLOOKUP(I14,$A$12:$E$15,4,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="inlineStr">
+      <c r="A15" s="49" t="inlineStr">
         <is>
           <t>Senior</t>
         </is>
       </c>
-      <c r="B15" s="139">
+      <c r="B15" s="50">
         <f>1.4*B6</f>
         <v/>
       </c>
-      <c r="C15" s="139">
+      <c r="C15" s="50">
         <f>1.4*C6</f>
         <v/>
       </c>
-      <c r="D15" s="139">
+      <c r="D15" s="50">
         <f>1.4*D6</f>
         <v/>
       </c>
-      <c r="E15" s="139">
+      <c r="E15" s="50">
         <f>1.4*E6</f>
         <v/>
       </c>
-      <c r="G15" s="50" t="n"/>
-      <c r="H15" s="45" t="inlineStr">
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="44" t="inlineStr">
         <is>
           <t>Leandro</t>
         </is>
       </c>
-      <c r="I15" s="45" t="inlineStr">
+      <c r="I15" s="44" t="inlineStr">
         <is>
           <t>Senior</t>
         </is>
       </c>
-      <c r="J15" s="141">
+      <c r="J15" s="46">
         <f>VLOOKUP(I15,$A$3:$E$6,3,0)</f>
         <v/>
       </c>
-      <c r="K15" s="141">
+      <c r="K15" s="46">
         <f>VLOOKUP(I15,$A$12:$E$15,3,0)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="H16" s="45" t="inlineStr">
+      <c r="H16" s="44" t="inlineStr">
         <is>
           <t>Simas</t>
         </is>
       </c>
-      <c r="I16" s="45" t="inlineStr">
+      <c r="I16" s="44" t="inlineStr">
         <is>
           <t>Junior</t>
         </is>
       </c>
-      <c r="J16" s="141">
+      <c r="J16" s="46">
         <f>VLOOKUP(I16,$A$3:$E$6,3,0)</f>
         <v/>
       </c>
-      <c r="K16" s="141">
+      <c r="K16" s="46">
         <f>VLOOKUP(I16,$A$12:$E$15,3,0)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="H17" s="79" t="inlineStr">
+      <c r="H17" s="77" t="inlineStr">
         <is>
           <t>Alvaro</t>
         </is>
       </c>
-      <c r="I17" s="45" t="inlineStr">
+      <c r="I17" s="44" t="inlineStr">
         <is>
           <t>Estagiário</t>
         </is>
       </c>
-      <c r="J17" s="141">
+      <c r="J17" s="46">
         <f>VLOOKUP(I17,$A$3:$E$6,3,0)</f>
         <v/>
       </c>
-      <c r="K17" s="141">
+      <c r="K17" s="46">
         <f>VLOOKUP(I17,$A$12:$E$15,3,0)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="115" t="inlineStr">
+      <c r="A18" s="113" t="inlineStr">
         <is>
           <t>Consultores Externos</t>
         </is>
       </c>
-      <c r="H18" s="45" t="inlineStr">
+      <c r="H18" s="44" t="inlineStr">
         <is>
           <t>Burato</t>
         </is>
       </c>
-      <c r="I18" s="45" t="inlineStr">
+      <c r="I18" s="44" t="inlineStr">
         <is>
           <t>Externo</t>
         </is>
       </c>
-      <c r="J18" s="141" t="n">
+      <c r="J18" s="46" t="n">
         <v>150</v>
       </c>
-      <c r="K18" s="141" t="n">
+      <c r="K18" s="46" t="n">
         <v>150</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="46" t="inlineStr">
+      <c r="A19" s="45" t="inlineStr">
         <is>
           <t>Carlos Burato</t>
         </is>
       </c>
-      <c r="B19" s="141" t="n">
+      <c r="B19" s="46" t="n">
         <v>150</v>
       </c>
-      <c r="H19" s="45" t="inlineStr">
+      <c r="H19" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">Marcio </t>
         </is>
       </c>
-      <c r="I19" s="45" t="inlineStr">
+      <c r="I19" s="44" t="inlineStr">
         <is>
           <t>Externo</t>
         </is>
       </c>
-      <c r="J19" s="141" t="n">
+      <c r="J19" s="46" t="n">
         <v>100</v>
       </c>
-      <c r="K19" s="141" t="n">
+      <c r="K19" s="46" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="46" t="inlineStr">
+      <c r="A20" s="45" t="inlineStr">
         <is>
           <t>Marcelo Guerra</t>
         </is>
       </c>
-      <c r="B20" s="141" t="n">
+      <c r="B20" s="46" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="46" t="inlineStr">
+      <c r="A21" s="45" t="inlineStr">
         <is>
           <t>Marcio Demétrio</t>
         </is>
       </c>
-      <c r="B21" s="141" t="n">
+      <c r="B21" s="46" t="n">
         <v>100</v>
       </c>
     </row>
